--- a/Anbin-Aravanaippu-Arakkattalai/contact-messages.xlsx
+++ b/Anbin-Aravanaippu-Arakkattalai/contact-messages.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="11">
   <si>
     <t>S.No.</t>
   </si>
@@ -89,7 +89,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -212,6 +212,66 @@
         <v>10</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E8" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>8.0</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E9" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Anbin-Aravanaippu-Arakkattalai/contact-messages.xlsx
+++ b/Anbin-Aravanaippu-Arakkattalai/contact-messages.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="11">
   <si>
     <t>S.No.</t>
   </si>
@@ -89,7 +89,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -272,6 +272,26 @@
         <v>10</v>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
